--- a/two-minute-training-tuesday/episodes/001-excel-dynamic-arrays/demo-workbook-solved.xlsx
+++ b/two-minute-training-tuesday/episodes/001-excel-dynamic-arrays/demo-workbook-solved.xlsx
@@ -11207,7 +11207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:M10"/>
+  <dimension ref="B1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -11326,6 +11326,15 @@
           <t>Shipping</t>
         </is>
       </c>
+    </row>
+    <row r="11">
+      <c r="M11" s="9" t="n"/>
+    </row>
+    <row r="12">
+      <c r="M12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="M13" s="9" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
